--- a/assets/downloads/assignment-tracker-template.xlsx
+++ b/assets/downloads/assignment-tracker-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="1" r:id="R5a06333b9bd54c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="1" r:id="Ree70008da7054781"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -330,8 +330,8 @@
       <x:c r="A3" s="1" t="str">
         <x:v>Reference date</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="d">
-        <x:v>2026-10-12T00:00:00.000Z</x:v>
+      <x:c r="B3" s="6" t="n">
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="C3" s="1"/>
       <x:c r="D3" s="1"/>
@@ -405,11 +405,11 @@
       <x:c r="B8" s="7" t="str">
         <x:v>Essay</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="d">
-        <x:v>2026-10-16T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="d">
-        <x:v>2026-10-12T00:00:00.000Z</x:v>
+      <x:c r="C8" s="8" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="n">
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>In progress</x:v>
@@ -432,11 +432,11 @@
       <x:c r="B9" s="7" t="str">
         <x:v>Problem set</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="d">
-        <x:v>2026-10-14T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="d">
-        <x:v>2026-10-12T00:00:00.000Z</x:v>
+      <x:c r="C9" s="8" t="n">
+        <x:v>46309</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="n">
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Not started</x:v>
@@ -459,11 +459,11 @@
       <x:c r="B10" s="7" t="str">
         <x:v>Presentation</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="d">
-        <x:v>2026-10-20T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="d">
-        <x:v>2026-10-15T00:00:00.000Z</x:v>
+      <x:c r="C10" s="8" t="n">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="n">
+        <x:v>46310</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Done</x:v>
